--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>23.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>11727.7</v>
+        <v>13242.47</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>53367.78</v>
+        <v>11727.7</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>103338.98</v>
+        <v>53367.78</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>119901.47</v>
+        <v>103338.98</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13419.0</t>
+          <t>7327.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>212.12</t>
+          <t>209.68</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>229.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>232.05</t>
+          <t>231.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-171.05</t>
+          <t>-175.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2548740.0</t>
+          <t>1350301.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1195856.8</t>
+          <t>1249637.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1117548.9</t>
+          <t>1108369.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>896532.4</t>
+          <t>880861.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>28591.23408475225</t>
+          <t>42638.96320575812</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>126307.99</v>
+        <v>119901.47</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>-29.10</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5013.0</t>
+          <t>13419.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-21.90</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>214.62</t>
+          <t>212.12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>232.96</t>
+          <t>231.32</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>232.48</t>
+          <t>232.05</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-167.75</t>
+          <t>-171.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1011717.0</t>
+          <t>2548740.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>892888.4</t>
+          <t>1195856.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>976034.8</t>
+          <t>1117548.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>893470.2</t>
+          <t>896532.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-83146</t>
+          <t>78307</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>10824.55153780596</t>
+          <t>28591.23408475225</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>2544.97</v>
+        <v>126307.99</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,42 +3332,42 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2935.0</t>
+          <t>5013.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-15.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>-21.90</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>207.6</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>214.62</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>233.97</t>
+          <t>232.96</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>232.64</t>
+          <t>232.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-166.65</t>
+          <t>-167.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>601143.0</t>
+          <t>1011717.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>910271.0</t>
+          <t>892888.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>917277.1</t>
+          <t>976034.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>894617.84</t>
+          <t>893470.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-7006</t>
+          <t>-83146</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>12329.92930197528</t>
+          <t>10824.55153780596</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-9669.190000000001</v>
+        <v>2544.97</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-19.92</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3612.0</t>
+          <t>2935.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-17.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.74</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>207.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>218.18</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>234.82</t>
+          <t>233.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>232.75</t>
+          <t>232.64</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-165.67</t>
+          <t>-166.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>736288.0</t>
+          <t>601143.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>939532.8</t>
+          <t>910271.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>934604.5</t>
+          <t>917277.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>900393.0</t>
+          <t>894617.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>-7006</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>16329.76889442319</t>
+          <t>12329.92930197528</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>17217.41</v>
+        <v>-9669.190000000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-19.92</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5139.0</t>
+          <t>3612.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-12.81</t>
+          <t>-16.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-20.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>208.1</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>219.6</t>
+          <t>218.18</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>235.73</t>
+          <t>234.82</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>232.83</t>
+          <t>232.75</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-164.38</t>
+          <t>-165.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1081396.0</t>
+          <t>736288.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>967102.0</t>
+          <t>939532.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>968166.7</t>
+          <t>934604.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>901485.7</t>
+          <t>900393.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1064</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>16168.37999197867</t>
+          <t>16329.76889442319</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>40532.1</v>
+        <v>17217.41</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-19.14</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4907.0</t>
+          <t>5139.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>-18.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.80</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>220.85</t>
+          <t>219.6</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>236.57</t>
+          <t>235.73</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>232.99</t>
+          <t>232.83</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-163.07</t>
+          <t>-164.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1033898.0</t>
+          <t>1081396.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1039241.0</t>
+          <t>967102.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>927474.6</t>
+          <t>968166.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>897989.24</t>
+          <t>901485.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>111766</t>
+          <t>-1064</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>11738.6122974249</t>
+          <t>16168.37999197867</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>35415.38</v>
+        <v>40532.1</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-18.16</t>
+          <t>-19.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5242.0</t>
+          <t>4907.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-19.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-17.83</t>
+          <t>-18.80</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>209.2</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>222.15</t>
+          <t>220.85</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>237.48</t>
+          <t>236.57</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>233.22</t>
+          <t>232.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-161.50</t>
+          <t>-163.07</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2591884.866859624</t>
+          <t>2590510.125</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1098630.0</t>
+          <t>1033898.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1059181.2</t>
+          <t>1039241.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>873798.4</t>
+          <t>927474.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>902286.02</t>
+          <t>897989.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>185382</t>
+          <t>111766</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7433.746087924741</t>
+          <t>11738.6122974249</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>31930</v>
+        <v>35415.38</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-14.37152843188938</t>
+          <t>-32.48808706458673</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>8.331352654369573</t>
+          <t>-34.21571608212139</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>33.64857459462222</t>
+          <t>21.33536864911409</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-9640.639999999999</v>
+        <v>-15379.43</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,42 +5918,42 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6008,17 +6008,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,220 +6181,220 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>409674.411849711</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>-9640.639999999999</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>5.51</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>410113.3198263387</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>-2763.38</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>12.76979097839344</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>17.1837120496049</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>10.33204910363525</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>5.53</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>7352.94</v>
+        <v>-2763.38</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6780,32 +6780,32 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,72 +6927,72 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>13700.33</v>
+        <v>7352.94</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,42 +7211,42 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2506.0</t>
+          <t>2424.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>133.65</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>137.92</t>
+          <t>138.05</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>129.72</t>
+          <t>129.85</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>-97.34</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-108.63</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>329556.0</t>
+          <t>310478.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>202843.0</t>
+          <t>232141.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>163571.8</t>
+          <t>181079.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>350070.6</t>
+          <t>355107.4</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-17631.44931081458</t>
+          <t>-12811.17557207666</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>5926.69</v>
+        <v>13700.33</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,42 +7642,42 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1784.0</t>
+          <t>2506.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,92 +7789,92 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>24.01</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>118.5</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,72 +7905,72 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>136.4</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>134.32</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>137.61</t>
+          <t>137.92</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>129.45</t>
+          <t>129.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>55.66</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>240225.0</t>
+          <t>329556.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>164139.2</t>
+          <t>202843.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>146289.3</t>
+          <t>163571.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>344833.18</t>
+          <t>350070.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-21914.74779137316</t>
+          <t>-17631.44931081458</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-7434.24</v>
+        <v>5926.69</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,27 +8073,27 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>132.5</t>
-        </is>
-      </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>137.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>962.0</t>
+          <t>1784.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>136.4</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>134.52</t>
+          <t>134.32</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>137.19</t>
+          <t>137.61</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>129.07</t>
+          <t>129.45</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>55.66</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.51</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>130193.0</t>
+          <t>240225.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>131395.6</t>
+          <t>164139.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>139923.4</t>
+          <t>146289.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>341817.6</t>
+          <t>344833.18</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-8527</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-24547.56678345393</t>
+          <t>-21914.74779137316</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-16684.61</v>
+        <v>-7434.24</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,42 +8504,42 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
           <t>138.0</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1115.0</t>
+          <t>962.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-27.68</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>74.81</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>136.1</t>
+          <t>135.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>134.52</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>136.83</t>
+          <t>137.19</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>128.76</t>
+          <t>129.07</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>26.24</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.51</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>150256.0</t>
+          <t>130193.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>124675.8</t>
+          <t>131395.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>172391.4</t>
+          <t>139923.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>343966.82</t>
+          <t>341817.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-47715</t>
+          <t>-8527</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-25977.19583024719</t>
+          <t>-24547.56678345393</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-17514.39</v>
+        <v>-16684.61</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,22 +8935,22 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
@@ -8960,17 +8960,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1202.0</t>
+          <t>1115.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,74 +9082,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-7.87</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-27.68</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-22.41</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>118.5</t>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>135.45</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>136.41</t>
+          <t>136.83</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>128.41</t>
+          <t>128.76</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.85</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>163985.0</t>
+          <t>150256.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>130017.0</t>
+          <t>124675.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>167560.7</t>
+          <t>172391.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>345184.66</t>
+          <t>343966.82</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-37543</t>
+          <t>-47715</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-27515.88768671462</t>
+          <t>-25977.19583024719</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-20223.89</v>
+        <v>-17514.39</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>1202.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,22 +9523,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.72</t>
+          <t>-22.41</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,79 +9629,79 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>74.44</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>135.45</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>136.41</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>128.07</t>
+          <t>128.41</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>-0.65</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>7.32</t>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-109.34</t>
+          <t>-108.85</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>136037.0</t>
+          <t>163985.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>124300.6</t>
+          <t>130017.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>160851.3</t>
+          <t>167560.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>344733.46</t>
+          <t>345184.66</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-36550</t>
+          <t>-37543</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28841.70563965835</t>
+          <t>-27515.88768671462</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-24843.28</v>
+        <v>-20223.89</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>135.5</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>134.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>568.0</t>
+          <t>999.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.33</t>
+          <t>-22.72</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>74.44</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>134.4</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>136.18</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>135.47</t>
+          <t>135.9</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>127.74</t>
+          <t>128.07</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-109.44</t>
+          <t>-109.34</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>410113.3198263387</t>
+          <t>409674.411849711</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>76507.0</t>
+          <t>136037.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>128439.4</t>
+          <t>124300.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>155366.7</t>
+          <t>160851.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>343993.18</t>
+          <t>344733.46</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-26927</t>
+          <t>-36550</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-29568.69150555039</t>
+          <t>-28841.70563965835</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-27560.73</v>
+        <v>-24843.28</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>12.76979097839344</t>
+          <t>3.377018673860202</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>17.1837120496049</t>
+          <t>37.82067205908043</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>10.33204910363525</t>
+          <t>18.0886033319889</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>228.01</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.70</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>202.12</t>
+          <t>199.58</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>223.18</t>
+          <t>221.65</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1021235.4</t>
+          <t>975725.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>879871.32</t>
+          <t>877001.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>13242.47</v>
+        <v>16149.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>23.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>11727.7</v>
+        <v>13242.47</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>53367.78</v>
+        <v>11727.7</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>103338.98</v>
+        <v>53367.78</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>119901.47</v>
+        <v>103338.98</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13419.0</t>
+          <t>7327.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>212.12</t>
+          <t>209.68</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>229.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>232.05</t>
+          <t>231.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-171.05</t>
+          <t>-175.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2548740.0</t>
+          <t>1350301.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1195856.8</t>
+          <t>1249637.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1117548.9</t>
+          <t>1108369.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>896532.4</t>
+          <t>880861.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>28591.23408475225</t>
+          <t>42638.96320575812</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>126307.99</v>
+        <v>119901.47</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>-29.10</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5013.0</t>
+          <t>13419.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-15.14</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-21.90</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>214.62</t>
+          <t>212.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>232.96</t>
+          <t>231.32</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>232.48</t>
+          <t>232.05</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-167.75</t>
+          <t>-171.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1011717.0</t>
+          <t>2548740.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>892888.4</t>
+          <t>1195856.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>976034.8</t>
+          <t>1117548.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>893470.2</t>
+          <t>896532.4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-83146</t>
+          <t>78307</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>10824.55153780596</t>
+          <t>28591.23408475225</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>2544.97</v>
+        <v>126307.99</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2935.0</t>
+          <t>5013.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-17.14</t>
+          <t>-17.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>-21.90</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>207.6</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>214.62</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>233.97</t>
+          <t>232.96</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>232.64</t>
+          <t>232.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-166.65</t>
+          <t>-167.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>601143.0</t>
+          <t>1011717.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>910271.0</t>
+          <t>892888.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>917277.1</t>
+          <t>976034.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>894617.84</t>
+          <t>893470.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-7006</t>
+          <t>-83146</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>12329.92930197528</t>
+          <t>10824.55153780596</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-9669.190000000001</v>
+        <v>2544.97</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-19.92</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3612.0</t>
+          <t>2935.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-19.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.74</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>207.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>218.18</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>234.82</t>
+          <t>233.97</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>232.75</t>
+          <t>232.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-165.67</t>
+          <t>-166.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>736288.0</t>
+          <t>601143.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>939532.8</t>
+          <t>910271.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>934604.5</t>
+          <t>917277.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>900393.0</t>
+          <t>894617.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>-7006</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>16329.76889442319</t>
+          <t>12329.92930197528</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>17217.41</v>
+        <v>-9669.190000000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-19.92</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5139.0</t>
+          <t>3612.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-18.29</t>
+          <t>-19.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-20.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>208.1</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>219.6</t>
+          <t>218.18</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>235.73</t>
+          <t>234.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>232.83</t>
+          <t>232.75</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-164.38</t>
+          <t>-165.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1081396.0</t>
+          <t>736288.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>967102.0</t>
+          <t>939532.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>968166.7</t>
+          <t>934604.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>901485.7</t>
+          <t>900393.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1064</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16168.37999197867</t>
+          <t>16329.76889442319</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>40532.1</v>
+        <v>17217.41</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-19.14</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4907.0</t>
+          <t>5139.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-18.80</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>208.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>220.85</t>
+          <t>219.6</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>236.57</t>
+          <t>235.73</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>232.99</t>
+          <t>232.83</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-163.07</t>
+          <t>-164.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2590510.125</t>
+          <t>2589202.20995671</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1033898.0</t>
+          <t>1081396.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1039241.0</t>
+          <t>967102.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>927474.6</t>
+          <t>968166.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>897989.24</t>
+          <t>901485.7</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>111766</t>
+          <t>-1064</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>11738.6122974249</t>
+          <t>16168.37999197867</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>35415.38</v>
+        <v>40532.1</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-18.16</t>
+          <t>-19.14</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>201404</t>
+          <t>196800</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>133.05</t>
+          <t>132.65</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>138.55</t>
+          <t>138.22</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>142080.0</t>
+          <t>103358.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>332412.34</t>
+          <t>306194.04</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-15379.43</v>
+        <v>-15566.3</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-9640.639999999999</v>
+        <v>-15379.43</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,220 +6612,220 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>409336.2164502165</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>-9640.639999999999</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>409674.411849711</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>-2763.38</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>5.51</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>7352.94</v>
+        <v>-2763.38</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,72 +7358,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-6.56</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-3.03</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>13700.33</v>
+        <v>7352.94</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2506.0</t>
+          <t>2424.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,162 +7920,162 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>133.65</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>138.05</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>129.85</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-97.34</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-108.63</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>409336.2164502165</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>310478.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>232141.6</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>181079.3</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>355107.4</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>51062</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-12811.17557207666</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>13700.33</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-2.77</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>135.6</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>134.1</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>137.92</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>129.72</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-106.53</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>409674.411849711</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>329556.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>202843.0</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>163571.8</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>350070.6</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>39271</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-17631.44931081458</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>5926.69</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>9.96</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM18" t="inlineStr">
         <is>
           <t>3.377018673860202</t>
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1784.0</t>
+          <t>2506.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,92 +8220,92 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-8.61</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>24.01</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-8.27</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-3.03</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>118.5</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,72 +8336,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>136.4</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>134.32</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>137.61</t>
+          <t>137.92</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>129.45</t>
+          <t>129.72</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>55.66</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>240225.0</t>
+          <t>329556.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>164139.2</t>
+          <t>202843.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>146289.3</t>
+          <t>163571.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>344833.18</t>
+          <t>350070.6</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-21914.74779137316</t>
+          <t>-17631.44931081458</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-7434.24</v>
+        <v>5926.69</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>132.5</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>137.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>962.0</t>
+          <t>1784.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-12.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>136.4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>134.52</t>
+          <t>134.32</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>137.19</t>
+          <t>137.61</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>129.07</t>
+          <t>129.45</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>55.66</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-107.51</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>130193.0</t>
+          <t>240225.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>131395.6</t>
+          <t>164139.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>139923.4</t>
+          <t>146289.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>341817.6</t>
+          <t>344833.18</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-8527</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-24547.56678345393</t>
+          <t>-21914.74779137316</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-16684.61</v>
+        <v>-7434.24</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
           <t>138.0</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1115.0</t>
+          <t>962.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-10.25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-27.68</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>74.81</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>136.1</t>
+          <t>135.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>134.52</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>136.83</t>
+          <t>137.19</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>128.76</t>
+          <t>129.07</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>26.24</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.51</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>150256.0</t>
+          <t>130193.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>124675.8</t>
+          <t>131395.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>172391.4</t>
+          <t>139923.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>343966.82</t>
+          <t>341817.6</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-47715</t>
+          <t>-8527</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-25977.19583024719</t>
+          <t>-24547.56678345393</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-17514.39</v>
+        <v>-16684.61</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1202.0</t>
+          <t>1115.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,74 +9513,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-12.3</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-27.68</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-7.48</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-3.03</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-22.41</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>118.5</t>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>135.45</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>136.41</t>
+          <t>136.83</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>128.41</t>
+          <t>128.76</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-108.85</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>163985.0</t>
+          <t>150256.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>130017.0</t>
+          <t>124675.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>167560.7</t>
+          <t>172391.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>345184.66</t>
+          <t>343966.82</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-37543</t>
+          <t>-47715</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-27515.88768671462</t>
+          <t>-25977.19583024719</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-20223.89</v>
+        <v>-17514.39</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>1202.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9954,27 +9954,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.72</t>
+          <t>-22.41</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>10.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,79 +10060,79 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>948</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>74.44</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>135.45</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>136.41</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>128.07</t>
+          <t>128.41</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.65</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>7.32</t>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-109.34</t>
+          <t>-108.85</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>409674.411849711</t>
+          <t>409336.2164502165</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>136037.0</t>
+          <t>163985.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>124300.6</t>
+          <t>130017.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>160851.3</t>
+          <t>167560.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>344733.46</t>
+          <t>345184.66</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-36550</t>
+          <t>-37543</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28841.70563965835</t>
+          <t>-27515.88768671462</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-24843.28</v>
+        <v>-20223.89</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>228.01</t>
+          <t>218.43</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,17 +10313,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>135.5</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>134.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>199.58</t>
+          <t>196.9</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>221.65</t>
+          <t>220.1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>975725.2</t>
+          <t>934593.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>877001.76</t>
+          <t>885517.86</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>16149.83</v>
+        <v>10342.65</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.70</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>202.12</t>
+          <t>199.58</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>223.18</t>
+          <t>221.65</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1021235.4</t>
+          <t>975725.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>879871.32</t>
+          <t>877001.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>13242.47</v>
+        <v>16149.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>23.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>11727.7</v>
+        <v>13242.47</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>53367.78</v>
+        <v>11727.7</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>103338.98</v>
+        <v>53367.78</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>119901.47</v>
+        <v>103338.98</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13419.0</t>
+          <t>7327.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>212.12</t>
+          <t>209.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>229.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>232.05</t>
+          <t>231.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-171.05</t>
+          <t>-175.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2548740.0</t>
+          <t>1350301.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1195856.8</t>
+          <t>1249637.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1117548.9</t>
+          <t>1108369.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>896532.4</t>
+          <t>880861.26</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>28591.23408475225</t>
+          <t>42638.96320575812</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>126307.99</v>
+        <v>119901.47</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>-29.10</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5013.0</t>
+          <t>13419.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-17.84</t>
+          <t>-9.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-21.90</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>214.62</t>
+          <t>212.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>232.96</t>
+          <t>231.32</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>232.48</t>
+          <t>232.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-167.75</t>
+          <t>-171.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1011717.0</t>
+          <t>2548740.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>892888.4</t>
+          <t>1195856.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>976034.8</t>
+          <t>1117548.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>893470.2</t>
+          <t>896532.4</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-83146</t>
+          <t>78307</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>10824.55153780596</t>
+          <t>28591.23408475225</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>2544.97</v>
+        <v>126307.99</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2935.0</t>
+          <t>5013.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-19.88</t>
+          <t>-19.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>-21.90</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>207.6</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>214.62</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>233.97</t>
+          <t>232.96</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>232.64</t>
+          <t>232.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-166.65</t>
+          <t>-167.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>601143.0</t>
+          <t>1011717.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>910271.0</t>
+          <t>892888.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>917277.1</t>
+          <t>976034.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>894617.84</t>
+          <t>893470.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-7006</t>
+          <t>-83146</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>12329.92930197528</t>
+          <t>10824.55153780596</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-9669.190000000001</v>
+        <v>2544.97</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-19.92</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3612.0</t>
+          <t>2935.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-19.59</t>
+          <t>-21.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.74</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>207.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>218.18</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>234.82</t>
+          <t>233.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>232.75</t>
+          <t>232.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-165.67</t>
+          <t>-166.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>736288.0</t>
+          <t>601143.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>939532.8</t>
+          <t>910271.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>934604.5</t>
+          <t>917277.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>900393.0</t>
+          <t>894617.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>-7006</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16329.76889442319</t>
+          <t>12329.92930197528</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>17217.41</v>
+        <v>-9669.190000000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-19.92</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5139.0</t>
+          <t>3612.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-21.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-20.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>208.1</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>219.6</t>
+          <t>218.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>235.73</t>
+          <t>234.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>232.83</t>
+          <t>232.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-164.38</t>
+          <t>-165.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2589202.20995671</t>
+          <t>2587683.695965418</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1081396.0</t>
+          <t>736288.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>967102.0</t>
+          <t>939532.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>968166.7</t>
+          <t>934604.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>901485.7</t>
+          <t>900393.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1064</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16168.37999197867</t>
+          <t>16329.76889442319</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>40532.1</v>
+        <v>17217.41</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-19.14</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>196800</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>204.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>132.65</t>
+          <t>132.12</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>137.82</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>103358.4</t>
+          <t>88131.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>306194.04</t>
+          <t>276222.6</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-15566.3</v>
+        <v>-17943.76</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5943,17 +5943,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>133.05</t>
+          <t>132.65</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>138.55</t>
+          <t>138.22</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>142080.0</t>
+          <t>103358.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>332412.34</t>
+          <t>306194.04</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-15379.43</v>
+        <v>-15566.3</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-9640.639999999999</v>
+        <v>-15379.43</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6870,17 +6870,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,220 +7043,220 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>408923.0360230548</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>-9640.639999999999</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>409336.2164502165</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>-2763.38</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>5.74</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>7352.94</v>
+        <v>-2763.38</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,72 +7789,72 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-7.44</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>13700.33</v>
+        <v>7352.94</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2506.0</t>
+          <t>2424.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>133.65</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>137.92</t>
+          <t>138.05</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>129.72</t>
+          <t>129.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>-97.34</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-108.63</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>329556.0</t>
+          <t>310478.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>202843.0</t>
+          <t>232141.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>163571.8</t>
+          <t>181079.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>350070.6</t>
+          <t>355107.4</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-17631.44931081458</t>
+          <t>-12811.17557207666</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>5926.69</v>
+        <v>13700.33</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1784.0</t>
+          <t>2506.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,92 +8651,92 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24.01</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-12.7</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>118.5</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,72 +8767,72 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>136.4</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>134.32</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>137.61</t>
+          <t>137.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>129.45</t>
+          <t>129.72</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>55.66</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>240225.0</t>
+          <t>329556.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>164139.2</t>
+          <t>202843.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>146289.3</t>
+          <t>163571.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>344833.18</t>
+          <t>350070.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-21914.74779137316</t>
+          <t>-17631.44931081458</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-7434.24</v>
+        <v>5926.69</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>132.5</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>137.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>962.0</t>
+          <t>1784.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.25</t>
+          <t>-13.64</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>136.4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>134.52</t>
+          <t>134.32</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>137.19</t>
+          <t>137.61</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>129.07</t>
+          <t>129.45</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>55.66</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-107.51</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>130193.0</t>
+          <t>240225.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>131395.6</t>
+          <t>164139.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>139923.4</t>
+          <t>146289.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>341817.6</t>
+          <t>344833.18</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-8527</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-24547.56678345393</t>
+          <t>-21914.74779137316</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-16684.61</v>
+        <v>-7434.24</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
           <t>138.0</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1115.0</t>
+          <t>962.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.3</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-27.68</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>74.81</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>136.1</t>
+          <t>135.9</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>134.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>136.83</t>
+          <t>137.19</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>128.76</t>
+          <t>129.07</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>26.24</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.51</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>150256.0</t>
+          <t>130193.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>124675.8</t>
+          <t>131395.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>172391.4</t>
+          <t>139923.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>343966.82</t>
+          <t>341817.6</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-47715</t>
+          <t>-8527</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-25977.19583024719</t>
+          <t>-24547.56678345393</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-17514.39</v>
+        <v>-16684.61</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1202.0</t>
+          <t>1115.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,74 +9944,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-13.22</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-27.68</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-11.89</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-22.41</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>118.5</t>
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>668</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>136.1</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>135.45</t>
+          <t>134.98</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>136.41</t>
+          <t>136.83</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>128.41</t>
+          <t>128.76</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.85</t>
+          <t>-108.00</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>409336.2164502165</t>
+          <t>408923.0360230548</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>163985.0</t>
+          <t>150256.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>130017.0</t>
+          <t>124675.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>167560.7</t>
+          <t>172391.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>345184.66</t>
+          <t>343966.82</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-37543</t>
+          <t>-47715</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-27515.88768671462</t>
+          <t>-25977.19583024719</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-20223.89</v>
+        <v>-17514.39</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>218.43</t>
+          <t>214.16</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>195.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>220.1</t>
+          <t>218.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>934593.2</t>
+          <t>959935.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>885517.86</t>
+          <t>889723.42</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>10342.65</v>
+        <v>-4846.93</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>199.58</t>
+          <t>196.9</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>221.65</t>
+          <t>220.1</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>975725.2</t>
+          <t>934593.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>877001.76</t>
+          <t>885517.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>16149.83</v>
+        <v>10342.65</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.70</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>202.12</t>
+          <t>199.58</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>223.18</t>
+          <t>221.65</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1021235.4</t>
+          <t>975725.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>879871.32</t>
+          <t>877001.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>13242.47</v>
+        <v>16149.83</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>23.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>11727.7</v>
+        <v>13242.47</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>53367.78</v>
+        <v>11727.7</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>103338.98</v>
+        <v>53367.78</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>119901.47</v>
+        <v>103338.98</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13419.0</t>
+          <t>7327.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.47</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>212.12</t>
+          <t>209.68</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>229.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>232.05</t>
+          <t>231.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-171.05</t>
+          <t>-175.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2548740.0</t>
+          <t>1350301.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1195856.8</t>
+          <t>1249637.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1117548.9</t>
+          <t>1108369.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>896532.4</t>
+          <t>880861.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>28591.23408475225</t>
+          <t>42638.96320575812</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>126307.99</v>
+        <v>119901.47</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>-29.10</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5013.0</t>
+          <t>13419.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-19.23</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.90</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>214.62</t>
+          <t>212.12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>232.96</t>
+          <t>231.32</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>232.48</t>
+          <t>232.05</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-167.75</t>
+          <t>-171.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1011717.0</t>
+          <t>2548740.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>892888.4</t>
+          <t>1195856.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>976034.8</t>
+          <t>1117548.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>893470.2</t>
+          <t>896532.4</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-83146</t>
+          <t>78307</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>10824.55153780596</t>
+          <t>28591.23408475225</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2544.97</v>
+        <v>126307.99</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2935.0</t>
+          <t>5013.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-21.3</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>-21.90</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>207.6</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>214.62</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>233.97</t>
+          <t>232.96</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>232.64</t>
+          <t>232.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-166.65</t>
+          <t>-167.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>601143.0</t>
+          <t>1011717.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>910271.0</t>
+          <t>892888.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>917277.1</t>
+          <t>976034.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>894617.84</t>
+          <t>893470.2</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-7006</t>
+          <t>-83146</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>12329.92930197528</t>
+          <t>10824.55153780596</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-9669.190000000001</v>
+        <v>2544.97</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-19.92</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>199.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3612.0</t>
+          <t>2935.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-21.01</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.74</t>
+          <t>-20.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>207.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>218.18</t>
+          <t>216.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>234.82</t>
+          <t>233.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>232.75</t>
+          <t>232.64</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.85</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-165.67</t>
+          <t>-166.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2587683.695965418</t>
+          <t>2585856.861151079</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>736288.0</t>
+          <t>601143.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>939532.8</t>
+          <t>910271.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>934604.5</t>
+          <t>917277.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>900393.0</t>
+          <t>894617.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>-7006</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16329.76889442319</t>
+          <t>12329.92930197528</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>17217.41</v>
+        <v>-9669.190000000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-19.92</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.52</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>213488</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>206.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>132.12</t>
+          <t>131.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>137.82</t>
+          <t>137.37</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>88131.8</t>
+          <t>95199.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>276222.6</t>
+          <t>258672.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-17943.76</v>
+        <v>-16288.53</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>132.65</t>
+          <t>132.12</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>137.82</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>103358.4</t>
+          <t>88131.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>306194.04</t>
+          <t>276222.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-15566.3</v>
+        <v>-17943.76</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>133.05</t>
+          <t>132.65</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>138.55</t>
+          <t>138.22</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>142080.0</t>
+          <t>103358.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>332412.34</t>
+          <t>306194.04</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-15379.43</v>
+        <v>-15566.3</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-9640.639999999999</v>
+        <v>-15379.43</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7301,17 +7301,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7343,42 +7343,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>654.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-7.44</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,220 +7474,220 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>408593.6589928058</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>-9640.639999999999</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>5.53</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>408923.0360230548</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>-2763.38</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>5.79</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>7352.94</v>
+        <v>-2763.38</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,72 +8220,72 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-2.77</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-3.31</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-3.02</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>13700.33</v>
+        <v>7352.94</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2506.0</t>
+          <t>2424.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.5</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,162 +8782,162 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>133.65</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>138.05</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>129.85</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-97.34</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-108.63</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>408593.6589928058</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>310478.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>232141.6</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>181079.3</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>355107.4</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>51062</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-12811.17557207666</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>13700.33</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-2.77</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>135.6</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>134.1</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>137.92</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>129.72</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-106.53</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>408923.0360230548</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>329556.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>202843.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>163571.8</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>350070.6</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>39271</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-17631.44931081458</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>5926.69</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>9.96</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
           <t>3.377018673860202</t>
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1784.0</t>
+          <t>2506.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,92 +9082,92 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-4.74</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>24.01</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-13.64</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-3.02</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>118.5</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,72 +9198,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>136.4</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>134.32</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>137.61</t>
+          <t>137.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>129.45</t>
+          <t>129.72</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>55.66</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>240225.0</t>
+          <t>329556.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>164139.2</t>
+          <t>202843.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>146289.3</t>
+          <t>163571.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>344833.18</t>
+          <t>350070.6</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-21914.74779137316</t>
+          <t>-17631.44931081458</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-7434.24</v>
+        <v>5926.69</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>132.5</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
           <t>32.86</t>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>962.0</t>
+          <t>1784.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-8.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>15.64</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>136.4</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>134.52</t>
+          <t>134.32</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>137.19</t>
+          <t>137.61</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>129.07</t>
+          <t>129.45</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>55.66</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.51</t>
+          <t>-106.59</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>130193.0</t>
+          <t>240225.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>131395.6</t>
+          <t>164139.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>139923.4</t>
+          <t>146289.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>341817.6</t>
+          <t>344833.18</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-8527</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-24547.56678345393</t>
+          <t>-21914.74779137316</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-16684.61</v>
+        <v>-7434.24</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
           <t>138.0</t>
         </is>
       </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1115.0</t>
+          <t>962.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-27.68</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>951</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>74.81</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>136.1</t>
+          <t>135.9</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>134.98</t>
+          <t>134.52</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>136.83</t>
+          <t>137.19</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>128.76</t>
+          <t>129.07</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>26.24</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.00</t>
+          <t>-107.51</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>408923.0360230548</t>
+          <t>408593.6589928058</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>150256.0</t>
+          <t>130193.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>124675.8</t>
+          <t>131395.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>172391.4</t>
+          <t>139923.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>343966.82</t>
+          <t>341817.6</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-47715</t>
+          <t>-8527</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-25977.19583024719</t>
+          <t>-24547.56678345393</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-17514.39</v>
+        <v>-16684.61</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>194.1</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>217.7</t>
+          <t>216.61</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1993876.8</t>
+          <t>2507410.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>998034.7</t>
+          <t>1052280.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5850667</v>
+        <v>3661376</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>195.25</t>
+          <t>194.1</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>218.81</t>
+          <t>217.7</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>959935.8</t>
+          <t>1993876.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>889723.42</t>
+          <t>998034.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>878689</v>
+        <v>5850667</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>195.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>220.1</t>
+          <t>218.81</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>934593.2</t>
+          <t>959935.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>885517.86</t>
+          <t>889723.42</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1023569</v>
+        <v>878689</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>199.58</t>
+          <t>196.9</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>221.65</t>
+          <t>220.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>975725.2</t>
+          <t>934593.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>877001.76</t>
+          <t>885517.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1122750</v>
+        <v>1023569</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>202.12</t>
+          <t>199.58</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>223.18</t>
+          <t>221.65</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1021235.4</t>
+          <t>975725.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>879871.32</t>
+          <t>877001.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1093709</v>
+        <v>1122750</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11727.69617533358</t>
+          <t>13242.47091378178</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>680962</v>
+        <v>1093709</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>53367.77882843139</t>
+          <t>11727.69617533358</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>751976</v>
+        <v>680962</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>103338.9762318416</t>
+          <t>53367.77882843139</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1229229</v>
+        <v>751976</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>119901.4733712904</t>
+          <t>103338.9762318416</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1350301</v>
+        <v>1229229</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13419.0</t>
+          <t>7327.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>24.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>212.12</t>
+          <t>209.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>229.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>232.05</t>
+          <t>231.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-171.05</t>
+          <t>-175.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2548740.0</t>
+          <t>1350301.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1195856.8</t>
+          <t>1249637.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1117548.9</t>
+          <t>1108369.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>896532.4</t>
+          <t>880861.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>28591.23408475225</t>
+          <t>42638.96320575812</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>126307.9880929568</t>
+          <t>119901.4733712904</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2548740</v>
+        <v>1350301</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>-29.10</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5013.0</t>
+          <t>13419.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-21.90</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.68</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>200.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>214.62</t>
+          <t>212.12</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>232.96</t>
+          <t>231.32</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>232.48</t>
+          <t>232.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-167.75</t>
+          <t>-171.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2594750.745689655</t>
+          <t>2598907.579626973</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1011717.0</t>
+          <t>2548740.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>892888.4</t>
+          <t>1195856.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>976034.8</t>
+          <t>1117548.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>893470.2</t>
+          <t>896532.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-83146</t>
+          <t>78307</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>10824.55153780596</t>
+          <t>28591.23408475225</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2544.973834874691</t>
+          <t>126307.9880929568</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1011717</v>
+        <v>2548740</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,27 +5810,27 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -5840,47 +5840,47 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>136.86</t>
+          <t>136.32</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>100397.6</t>
+          <t>98412.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>246240.56</t>
+          <t>232237.94</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>112462</v>
+        <v>61001</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6073,17 +6073,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>131.57</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>136.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>95199.0</t>
+          <t>100397.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>258672.3</t>
+          <t>246240.56</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>120004</v>
+        <v>112462</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>132.12</t>
+          <t>131.57</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>137.82</t>
+          <t>137.37</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>88131.8</t>
+          <t>95199.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>276222.6</t>
+          <t>258672.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>81726</v>
+        <v>120004</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>132.65</t>
+          <t>132.12</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>137.82</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>103358.4</t>
+          <t>88131.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>306194.04</t>
+          <t>276222.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>116870</v>
+        <v>81726</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>133.05</t>
+          <t>132.65</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>138.55</t>
+          <t>138.22</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>142080.0</t>
+          <t>103358.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>332412.34</t>
+          <t>306194.04</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>70926</v>
+        <v>116870</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-9640.640469615755</t>
+          <t>-15379.43437848878</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>86469</v>
+        <v>70926</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,225 +8426,225 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>407794.5301291248</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-9640.640469615755</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>86469</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>408248.974137931</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-2763.376297310897</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>84668</v>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>7352.943102314282</t>
+          <t>-2763.376297310897</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>157859</v>
+        <v>84668</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,12 +9055,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,72 +9182,72 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>13700.32999098187</t>
+          <t>7352.943102314282</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>310478</v>
+        <v>157859</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2506.0</t>
+          <t>2424.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>133.65</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>137.92</t>
+          <t>138.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>129.72</t>
+          <t>129.85</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>-97.34</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-108.63</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>329556.0</t>
+          <t>310478.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>202843.0</t>
+          <t>232141.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>163571.8</t>
+          <t>181079.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>350070.6</t>
+          <t>355107.4</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-17631.44931081458</t>
+          <t>-12811.17557207666</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>5926.692332257662</t>
+          <t>13700.32999098187</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>329556</v>
+        <v>310478</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1784.0</t>
+          <t>2506.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,92 +10054,92 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>24.01</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-9.56</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>12.20</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>118.5</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,72 +10170,72 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>489</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>136.4</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>134.32</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>137.61</t>
+          <t>137.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>129.45</t>
+          <t>129.72</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>55.66</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.59</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>408248.974137931</t>
+          <t>407794.5301291248</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>240225.0</t>
+          <t>329556.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>164139.2</t>
+          <t>202843.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>146289.3</t>
+          <t>163571.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>344833.18</t>
+          <t>350070.6</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-21914.74779137316</t>
+          <t>-17631.44931081458</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-7434.243334928964</t>
+          <t>5926.692332257662</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>240225</v>
+        <v>329556</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>211.14</t>
+          <t>218.09</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,24 +10428,24 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>132.5</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
       <c r="CH23" t="inlineStr">
         <is>
           <t>32.86</t>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>216.61</t>
+          <t>215.57</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2507410.2</t>
+          <t>2544647.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1052280.38</t>
+          <t>1063589.72</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3661376</v>
+        <v>1308934</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>194.1</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>217.7</t>
+          <t>216.61</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1993876.8</t>
+          <t>2507410.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>998034.7</t>
+          <t>1052280.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5850667</v>
+        <v>3661376</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>195.25</t>
+          <t>194.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>218.81</t>
+          <t>217.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>959935.8</t>
+          <t>1993876.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>889723.42</t>
+          <t>998034.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>878689</v>
+        <v>5850667</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>195.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>220.1</t>
+          <t>218.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>934593.2</t>
+          <t>959935.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>885517.86</t>
+          <t>889723.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1023569</v>
+        <v>878689</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>199.58</t>
+          <t>196.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>221.65</t>
+          <t>220.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>975725.2</t>
+          <t>934593.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>877001.76</t>
+          <t>885517.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1122750</v>
+        <v>1023569</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>202.12</t>
+          <t>199.58</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>223.18</t>
+          <t>221.65</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1021235.4</t>
+          <t>975725.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>879871.32</t>
+          <t>877001.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1093709</v>
+        <v>1122750</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11727.69617533358</t>
+          <t>13242.47091378178</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>680962</v>
+        <v>1093709</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>53367.77882843139</t>
+          <t>11727.69617533358</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>751976</v>
+        <v>680962</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>103338.9762318416</t>
+          <t>53367.77882843139</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1229229</v>
+        <v>751976</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>119901.4733712904</t>
+          <t>103338.9762318416</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1350301</v>
+        <v>1229229</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13419.0</t>
+          <t>7327.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>24.38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>200.6</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>212.12</t>
+          <t>209.68</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>229.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>232.05</t>
+          <t>231.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-171.05</t>
+          <t>-175.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2598907.579626973</t>
+          <t>2597997.111747851</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2548740.0</t>
+          <t>1350301.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1195856.8</t>
+          <t>1249637.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1117548.9</t>
+          <t>1108369.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>896532.4</t>
+          <t>880861.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>28591.23408475225</t>
+          <t>42638.96320575812</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>126307.9880929568</t>
+          <t>119901.4733712904</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2548740</v>
+        <v>1350301</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>-29.10</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>219818</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,69 +5694,69 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>130.57</t>
+          <t>130.43</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>136.32</t>
+          <t>135.91</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>98412.6</t>
+          <t>94759.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>232237.94</t>
+          <t>221528.96</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>61001</v>
+        <v>98606</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,27 +6246,27 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -6276,47 +6276,47 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.57</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>136.86</t>
+          <t>136.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>100397.6</t>
+          <t>98412.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>246240.56</t>
+          <t>232237.94</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>112462</v>
+        <v>61001</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6509,17 +6509,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>131.57</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>136.86</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>95199.0</t>
+          <t>100397.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>258672.3</t>
+          <t>246240.56</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>120004</v>
+        <v>112462</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>132.12</t>
+          <t>131.57</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>137.82</t>
+          <t>137.37</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>88131.8</t>
+          <t>95199.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>276222.6</t>
+          <t>258672.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>81726</v>
+        <v>120004</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>132.65</t>
+          <t>132.12</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>137.82</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>103358.4</t>
+          <t>88131.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>306194.04</t>
+          <t>276222.6</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>116870</v>
+        <v>81726</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7752,17 +7752,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>133.05</t>
+          <t>132.65</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>138.55</t>
+          <t>138.22</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>142080.0</t>
+          <t>103358.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>332412.34</t>
+          <t>306194.04</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>70926</v>
+        <v>116870</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-9640.640469615755</t>
+          <t>-15379.43437848878</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>86469</v>
+        <v>70926</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8689,17 +8689,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,225 +8862,225 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>407422.2012893982</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-9640.640469615755</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>86469</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>407794.5301291248</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>-2763.376297310897</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>84668</v>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>7352.943102314282</t>
+          <t>-2763.376297310897</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>157859</v>
+        <v>84668</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,72 +9618,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>13700.32999098187</t>
+          <t>7352.943102314282</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>310478</v>
+        <v>157859</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2506.0</t>
+          <t>2424.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>771</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>133.65</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>137.92</t>
+          <t>138.05</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>129.72</t>
+          <t>129.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>-97.34</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-108.63</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>407794.5301291248</t>
+          <t>407422.2012893982</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>329556.0</t>
+          <t>310478.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>202843.0</t>
+          <t>232141.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>163571.8</t>
+          <t>181079.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>350070.6</t>
+          <t>355107.4</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-17631.44931081458</t>
+          <t>-12811.17557207666</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>5926.692332257662</t>
+          <t>13700.32999098187</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>329556</v>
+        <v>310478</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>218.09</t>
+          <t>225.11</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6845.0</t>
+          <t>4936.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,245 +1014,245 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>92.73</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>87.27</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-10.72</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-5.62</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>192.2</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>191.62</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>214.64</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>227.42</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>25.96</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-10.28</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>11.18</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-191.94</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2596339.993562232</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>959781.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2531889.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>1733241.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>1067656.78</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>798648</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>163405.0926673785</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>181494.8502325097</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>959781</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-24.02</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-32.48808706458673</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-34.21571608212139</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>21.33536864911409</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>55.97%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>34.92%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
           <t>89.09</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>89.7</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-2.67</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-10.83</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-5.27</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>187.1</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>192.22</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>215.57</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>227.57</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-8.74</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-10.95</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>11.18</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-197.91</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>2597997.111747851</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1308934.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2544647.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>1760186.1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1063589.72</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>784460</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>160116.0458373547</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>307065.1071884141</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>1308934</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>256.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-24.41</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>元太</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>元太</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-32.48808706458673</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-34.21571608212139</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>21.33536864911409</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>55.97%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>34.92%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>86.4</t>
-        </is>
-      </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>192.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>216.61</t>
+          <t>215.57</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2507410.2</t>
+          <t>2544647.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1052280.38</t>
+          <t>1063589.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3661376</v>
+        <v>1308934</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>194.1</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>217.7</t>
+          <t>216.61</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1993876.8</t>
+          <t>2507410.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>998034.7</t>
+          <t>1052280.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5850667</v>
+        <v>3661376</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>195.25</t>
+          <t>194.1</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>218.81</t>
+          <t>217.7</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>959935.8</t>
+          <t>1993876.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>889723.42</t>
+          <t>998034.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>878689</v>
+        <v>5850667</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>196.9</t>
+          <t>195.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>220.1</t>
+          <t>218.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>934593.2</t>
+          <t>959935.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>885517.86</t>
+          <t>889723.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1023569</v>
+        <v>878689</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>199.58</t>
+          <t>196.9</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>221.65</t>
+          <t>220.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>975725.2</t>
+          <t>934593.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>877001.76</t>
+          <t>885517.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1122750</v>
+        <v>1023569</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>202.12</t>
+          <t>199.58</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>223.18</t>
+          <t>221.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1021235.4</t>
+          <t>975725.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>879871.32</t>
+          <t>877001.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1093709</v>
+        <v>1122750</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>204.22</t>
+          <t>202.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>224.64</t>
+          <t>223.18</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1312241.6</t>
+          <t>1021235.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>886581.5</t>
+          <t>879871.32</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>11727.69617533358</t>
+          <t>13242.47091378178</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>680962</v>
+        <v>1093709</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>206.1</t>
+          <t>204.22</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>224.64</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1378392.6</t>
+          <t>1312241.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>885522.98</t>
+          <t>886581.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>53367.77882843139</t>
+          <t>11727.69617533358</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>751976</v>
+        <v>680962</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>207.85</t>
+          <t>206.1</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>227.79</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1348226.0</t>
+          <t>1378392.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>889533.12</t>
+          <t>885522.98</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>103338.9762318416</t>
+          <t>53367.77882843139</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1229229</v>
+        <v>751976</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7327.0</t>
+          <t>6739.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>209.68</t>
+          <t>207.85</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>229.52</t>
+          <t>227.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>231.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-175.90</t>
+          <t>-181.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2597997.111747851</t>
+          <t>2596339.993562232</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1350301.0</t>
+          <t>1229229.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1249637.8</t>
+          <t>1348226.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1108369.9</t>
+          <t>1143879.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>880861.26</t>
+          <t>889533.12</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>204346</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>42638.96320575812</t>
+          <t>51977.4267482325</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>119901.4733712904</t>
+          <t>103338.9762318416</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1350301</v>
+        <v>1229229</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>182.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>771.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>130.43</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>135.91</t>
+          <t>135.62</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>131.31</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,56 +5890,56 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.80</t>
+          <t>-133.84</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>94759.8</t>
+          <t>94407.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>99059.1</t>
+          <t>91269.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>221528.96</t>
+          <t>207737.7</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4299</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-14182.36959019367</t>
+          <t>-14583.18767553882</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-16737.5513580027</t>
+          <t>-16787.68714493714</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>98606</v>
+        <v>79964</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,69 +6130,69 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>0</t>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>130.57</t>
+          <t>130.43</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>136.32</t>
+          <t>135.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,56 +6326,56 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>98412.6</t>
+          <t>94759.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>232237.94</t>
+          <t>221528.96</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>61001</v>
+        <v>98606</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,27 +6682,27 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -6712,47 +6712,47 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.57</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>136.86</t>
+          <t>136.32</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,56 +6762,56 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>100397.6</t>
+          <t>98412.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>246240.56</t>
+          <t>232237.94</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>112462</v>
+        <v>61001</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6945,17 +6945,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>131.57</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>136.86</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,56 +7198,56 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>95199.0</t>
+          <t>100397.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>258672.3</t>
+          <t>246240.56</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>120004</v>
+        <v>112462</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>132.12</t>
+          <t>131.57</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>137.82</t>
+          <t>137.37</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,56 +7634,56 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>88131.8</t>
+          <t>95199.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>276222.6</t>
+          <t>258672.3</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>81726</v>
+        <v>120004</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>132.65</t>
+          <t>132.12</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>137.82</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,56 +8070,56 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>103358.4</t>
+          <t>88131.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>306194.04</t>
+          <t>276222.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>116870</v>
+        <v>81726</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8188,17 +8188,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>133.05</t>
+          <t>132.65</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>138.55</t>
+          <t>138.22</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,56 +8506,56 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>142080.0</t>
+          <t>103358.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>332412.34</t>
+          <t>306194.04</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>70926</v>
+        <v>116870</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>133.22</t>
+          <t>133.05</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>138.55</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,56 +8942,56 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>193806.0</t>
+          <t>142080.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>340328.8</t>
+          <t>332412.34</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-9640.640469615755</t>
+          <t>-15379.43437848878</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>86469</v>
+        <v>70926</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,225 +9298,225 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>133.22</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>138.53</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>407010.9334763949</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>193806.0</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>340328.8</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-9640.640469615755</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>86469</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>407422.2012893982</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>-2763.376297310897</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>84668</v>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>5.41</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,56 +9814,56 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>233662.2</t>
+          <t>224557.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>356682.06</t>
+          <t>352282.84</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>7352.943102314282</t>
+          <t>-2763.376297310897</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>157859</v>
+        <v>84668</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>1225.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,72 +10054,72 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>611</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.9</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>133.6</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>138.27</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>129.85</t>
+          <t>130.02</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-97.34</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,60 +10250,60 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.63</t>
+          <t>-110.87</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>407422.2012893982</t>
+          <t>407010.9334763949</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>310478.0</t>
+          <t>157859.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>232141.6</t>
+          <t>233662.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>181079.3</t>
+          <t>179169.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>355107.4</t>
+          <t>356682.06</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-12811.17557207666</t>
+          <t>-9709.003468324208</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>13700.32999098187</t>
+          <t>7352.943102314282</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>310478</v>
+        <v>157859</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>192.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>191.62</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>214.64</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>191.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>214.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>959781.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2531889.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>2531889.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1733241.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1067656.78</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1067656.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>181494.8502325097</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>959781</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>959781.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>187.1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>192.22</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>215.57</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>192.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>215.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1308934.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2544647.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2544647</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1760186.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1063589.72</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1063589.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>307065.1071884141</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1308934</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1308934.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>182.6</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>216.61</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>193</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>216.61</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3661376.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2507410.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2507410.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1764322.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1052280.38</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1052280.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>438075.3275829772</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3661376</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3661376.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>179.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>194.1</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>217.7</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>217.7</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>5850667.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1993876.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1993876.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1653059.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>998034.7</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>998034.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>357539.880732961</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>5850667</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>5850667.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>176.1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>195.25</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>218.81</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>218.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>878689.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>959935.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>959935.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1169164.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>889723.42</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>889723.42</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-4846.931936096633</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>878689</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>878689.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>175.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>196.9</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>220.1</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>220.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1023569.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>934593.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>934593.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1141409.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>885517.86</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>885517.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>10342.65467725322</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1023569</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1023569.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>178.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>199.58</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>221.65</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>199.58</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>221.65</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1122750.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>975725.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>975725.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1112681.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>877001.76</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>877001.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>16149.8264578511</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1122750</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1122750.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>180.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>202.12</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>223.18</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>202.12</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>223.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1093709.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1021235.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1021235.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1108546.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>879871.32</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>879871.3199999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>13242.47091378178</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1093709</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1093709.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>182.3</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>204.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>224.64</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>204.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>224.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>680962.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1312241.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1312241.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1102565.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>886581.5</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>886581.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>11727.69617533358</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>680962</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>680962.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>186.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>206.1</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>226.2</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>226.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>751976.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1378392.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1378392.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1144331.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>885522.98</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>885522.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>53367.77882843139</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>751976</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>751976.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>190.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>207.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>227.79</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>207.85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>227.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1229229.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1348226.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1348226</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1143879.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>889533.12</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>889533.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>103338.9762318416</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1229229</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1229229.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>127.5</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>135.62</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>135.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>79964.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>94407.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>94407.39999999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>91269.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>207737.7</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>207737.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-16787.68714493714</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>79964</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>79964.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>125.5</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>130.43</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>135.91</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>130.43</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>135.91</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>98606.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>94759.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>94759.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>99059.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>221528.96</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>221528.96</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-16737.5513580027</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>98606</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>98606.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>124.0</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>130.57</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>136.32</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>130.57</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>136.32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>61001.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>98412.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>98412.60000000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>120246.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>232237.94</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>232237.94</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-18065.51625673911</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>61001</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>61001.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>124.4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>136.86</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>131</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>136.86</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>112462.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>100397.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>100397.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>147101.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>246240.56</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>246240.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-15288.3048171933</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>112462</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>112462.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>131.57</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>137.37</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>131.57</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>137.37</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>120004.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>95199.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>95199</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>159878.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>258672.3</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>258672.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-16288.52758865671</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>120004</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>120004.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>125.3</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>132.12</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>137.82</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>132.12</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>137.82</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>81726.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>88131.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>88131.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>160897.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>276222.6</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>276222.6</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-17943.75556258095</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>81726</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>81726.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>127.1</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>132.65</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>138.22</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>132.65</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>138.22</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>116870.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>103358.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>103358.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>167750.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>306194.04</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>306194.04</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-15566.30425523766</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>116870</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>116870.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>127.7</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>133.05</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>138.55</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>138.55</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>70926.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>142080.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>142080</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>172461.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>332412.34</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>332412.34</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-15379.43437848878</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>70926</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>70926.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>128.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>133.22</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>138.53</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>133.22</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>138.53</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>86469.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>193806.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>193806</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>178972.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>340328.8</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>340328.8</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-9640.640469615755</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>86469</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>131.0</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>133.5</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>138.43</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>138.43</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>84668.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>224557.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>224557.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>177976.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>352282.84</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>352282.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-2763.376297310897</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>84668</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>84668.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>131.9</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>133.6</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>138.27</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>138.27</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>157859.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>233662.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>233662.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>179169.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>356682.06</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>356682.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>7352.943102314282</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>157859</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>157859.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4936.0</t>
+          <t>3911.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>92.73</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>192.2</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>191.62</v>
+        <v>191.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>214.64</v>
+        <v>213.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>227.42</t>
+          <t>227.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-191.94</t>
+          <t>-185.57</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2531889.4</v>
+        <v>2507368.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1733241.3</t>
+          <t>1733652.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1067656.78</v>
+        <v>1072476.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>798648</t>
+          <t>773716</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>163405.0926673785</t>
+          <t>149616.774427407</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>181494.8502325097</t>
+          <t>73781.02410756378</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-24.02</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>190.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>193.5</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>197.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>194.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6845.0</t>
+          <t>4936.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>92.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-10.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>192.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>192.22</v>
+        <v>191.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>215.57</v>
+        <v>214.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>227.57</t>
+          <t>227.42</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-197.91</t>
+          <t>-191.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2544647</v>
+        <v>2531889.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1760186.1</t>
+          <t>1733241.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1063589.72</v>
+        <v>1067656.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>784460</t>
+          <t>798648</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>160116.0458373547</t>
+          <t>163405.0926673785</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>307065.1071884141</t>
+          <t>181494.8502325097</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-24.02</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>193</v>
+        <v>192.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>216.61</v>
+        <v>215.57</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2507410.2</v>
+        <v>2544647</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1052280.38</v>
+        <v>1063589.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>194.1</v>
+        <v>193</v>
       </c>
       <c r="AN5" t="n">
-        <v>217.7</v>
+        <v>216.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1993876.8</v>
+        <v>2507410.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>998034.7</v>
+        <v>1052280.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>195.25</v>
+        <v>194.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>218.81</v>
+        <v>217.7</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>959935.8</v>
+        <v>1993876.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>889723.42</v>
+        <v>998034.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>196.9</v>
+        <v>195.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>220.1</v>
+        <v>218.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>934593.2</v>
+        <v>959935.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>885517.86</v>
+        <v>889723.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>199.58</v>
+        <v>196.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>221.65</v>
+        <v>220.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>975725.2</v>
+        <v>934593.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>877001.76</v>
+        <v>885517.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>202.12</v>
+        <v>199.58</v>
       </c>
       <c r="AN9" t="n">
-        <v>223.18</v>
+        <v>221.65</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1021235.4</v>
+        <v>975725.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>879871.3199999999</v>
+        <v>877001.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>204.22</v>
+        <v>202.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>224.64</v>
+        <v>223.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1312241.6</v>
+        <v>1021235.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>886581.5</v>
+        <v>879871.3199999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>11727.69617533358</t>
+          <t>13242.47091378178</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>206.1</v>
+        <v>204.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>226.2</v>
+        <v>224.64</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1378392.6</v>
+        <v>1312241.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>885522.98</v>
+        <v>886581.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>53367.77882843139</t>
+          <t>11727.69617533358</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6739.0</t>
+          <t>4085.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-28.88</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-9.46</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>190.9</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>207.85</v>
+        <v>206.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>227.79</v>
+        <v>226.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>231.01</t>
+          <t>230.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-181.30</t>
+          <t>-186.28</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2596339.993562232</t>
+          <t>2594251.116428572</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1348226</v>
+        <v>1378392.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1143879.4</t>
+          <t>1144331.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>889533.12</v>
+        <v>885522.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>204346</t>
+          <t>234060</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>51977.4267482325</t>
+          <t>52191.3270682631</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>103338.9762318416</t>
+          <t>53367.77882843139</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1229229.0</t>
+          <t>751976.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-29.10</t>
+          <t>-28.32</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>222695</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>130.2</v>
+        <v>129.98</v>
       </c>
       <c r="AN13" t="n">
-        <v>135.62</v>
+        <v>135.32</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>131.31</t>
+          <t>131.49</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-133.84</t>
+          <t>-132.00</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>94407.39999999999</v>
+        <v>81276.39999999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>91269.6</t>
+          <t>88237.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>207737.7</v>
+        <v>202045.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>-6961</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-14583.18767553882</t>
+          <t>-15158.73034348174</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-16787.68714493714</t>
+          <t>-18324.21501716781</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,19 +5996,19 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>130.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>771.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>130.43</v>
+        <v>130.2</v>
       </c>
       <c r="AN14" t="n">
-        <v>135.91</v>
+        <v>135.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>131.31</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.80</t>
+          <t>-133.84</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>94759.8</v>
+        <v>94407.39999999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>99059.1</t>
+          <t>91269.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>221528.96</v>
+        <v>207737.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4299</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-14182.36959019367</t>
+          <t>-14583.18767553882</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-16737.5513580027</t>
+          <t>-16787.68714493714</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,69 +6488,69 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>0</t>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>130.57</v>
+        <v>130.43</v>
       </c>
       <c r="AN15" t="n">
-        <v>136.32</v>
+        <v>135.91</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>98412.60000000001</v>
+        <v>94759.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>232237.94</v>
+        <v>221528.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,27 +7034,27 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -7064,43 +7064,43 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>131</v>
+        <v>130.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>136.86</v>
+        <v>136.32</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>100397.6</v>
+        <v>98412.60000000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>246240.56</v>
+        <v>232237.94</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>131.57</v>
+        <v>131</v>
       </c>
       <c r="AN17" t="n">
-        <v>137.37</v>
+        <v>136.86</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>95199</v>
+        <v>100397.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>258672.3</v>
+        <v>246240.56</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>132.12</v>
+        <v>131.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>137.82</v>
+        <v>137.37</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>88131.8</v>
+        <v>95199</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>276222.6</v>
+        <v>258672.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>132.65</v>
+        <v>132.12</v>
       </c>
       <c r="AN19" t="n">
-        <v>138.22</v>
+        <v>137.82</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>103358.4</v>
+        <v>88131.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>306194.04</v>
+        <v>276222.6</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>133.05</v>
+        <v>132.65</v>
       </c>
       <c r="AN20" t="n">
-        <v>138.55</v>
+        <v>138.22</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>142080</v>
+        <v>103358.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>332412.34</v>
+        <v>306194.04</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>133.22</v>
+        <v>133.05</v>
       </c>
       <c r="AN21" t="n">
-        <v>138.53</v>
+        <v>138.55</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>193806</v>
+        <v>142080</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>340328.8</v>
+        <v>332412.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-9640.640469615755</t>
+          <t>-15379.43437848878</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,216 +9614,216 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>133.22</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>138.53</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>406545.9514285715</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>193806</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>340328.8</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-9640.640469615755</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>138.43</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>407010.9334763949</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>224557.2</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>352282.84</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-2763.376297310897</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BV22" t="inlineStr">
         <is>
           <t>21.72</t>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1225.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>133.6</v>
+        <v>133.5</v>
       </c>
       <c r="AN23" t="n">
-        <v>138.27</v>
+        <v>138.43</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>130.02</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-66.76</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-110.87</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>407010.9334763949</t>
+          <t>406545.9514285715</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>233662.2</v>
+        <v>224557.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>179169.0</t>
+          <t>177976.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>356682.06</v>
+        <v>352282.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-9709.003468324208</t>
+          <t>-8640.445442014467</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>7352.943102314282</t>
+          <t>-2763.376297310897</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>157859.0</t>
+          <t>84668.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3911.0</t>
+          <t>3058.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>193.8</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>191.02</v>
+        <v>190.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>213.64</v>
+        <v>212.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>227.21</t>
+          <t>226.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-185.57</t>
+          <t>-179.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2507368.4</v>
+        <v>1455218</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1733652.1</t>
+          <t>1724547.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1072476.02</v>
+        <v>1071590.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>773716</t>
+          <t>-269329</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>149616.774427407</t>
+          <t>124148.6776258694</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>73781.02410756378</t>
+          <t>-15925.85478258738</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4936.0</t>
+          <t>3911.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>92.73</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>192.2</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>191.62</v>
+        <v>191.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>214.64</v>
+        <v>213.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>227.42</t>
+          <t>227.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-191.94</t>
+          <t>-185.57</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2531889.4</v>
+        <v>2507368.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1733241.3</t>
+          <t>1733652.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1067656.78</v>
+        <v>1072476.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>798648</t>
+          <t>773716</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>163405.0926673785</t>
+          <t>149616.774427407</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>181494.8502325097</t>
+          <t>73781.02410756378</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-24.02</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>190.5</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>193.5</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>197.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>194.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6845.0</t>
+          <t>4936.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>92.73</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-10.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>192.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>192.22</v>
+        <v>191.62</v>
       </c>
       <c r="AN4" t="n">
-        <v>215.57</v>
+        <v>214.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>227.57</t>
+          <t>227.42</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-197.91</t>
+          <t>-191.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2544647</v>
+        <v>2531889.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1760186.1</t>
+          <t>1733241.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1063589.72</v>
+        <v>1067656.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>784460</t>
+          <t>798648</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>160116.0458373547</t>
+          <t>163405.0926673785</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>307065.1071884141</t>
+          <t>181494.8502325097</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-24.02</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>193</v>
+        <v>192.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>216.61</v>
+        <v>215.57</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2507410.2</v>
+        <v>2544647</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1052280.38</v>
+        <v>1063589.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>194.1</v>
+        <v>193</v>
       </c>
       <c r="AN6" t="n">
-        <v>217.7</v>
+        <v>216.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1993876.8</v>
+        <v>2507410.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>998034.7</v>
+        <v>1052280.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>195.25</v>
+        <v>194.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>218.81</v>
+        <v>217.7</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>959935.8</v>
+        <v>1993876.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>889723.42</v>
+        <v>998034.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>196.9</v>
+        <v>195.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>220.1</v>
+        <v>218.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>934593.2</v>
+        <v>959935.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>885517.86</v>
+        <v>889723.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>199.58</v>
+        <v>196.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>221.65</v>
+        <v>220.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>975725.2</v>
+        <v>934593.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>877001.76</v>
+        <v>885517.86</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>202.12</v>
+        <v>199.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>223.18</v>
+        <v>221.65</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1021235.4</v>
+        <v>975725.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>879871.3199999999</v>
+        <v>877001.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>204.22</v>
+        <v>202.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>224.64</v>
+        <v>223.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1312241.6</v>
+        <v>1021235.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>886581.5</v>
+        <v>879871.3199999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>11727.69617533358</t>
+          <t>13242.47091378178</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4085.0</t>
+          <t>3781.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.88</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.46</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>182.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>206.1</v>
+        <v>204.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>226.2</v>
+        <v>224.64</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>230.58</t>
+          <t>230.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-20.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-186.28</t>
+          <t>-191.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2594251.116428572</t>
+          <t>2591812.630527818</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1378392.6</v>
+        <v>1312241.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1144331.8</t>
+          <t>1102565.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>885522.98</v>
+        <v>886581.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>234060</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>52191.3270682631</t>
+          <t>45966.15308473548</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>53367.77882843139</t>
+          <t>11727.69617533358</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>751976.0</t>
+          <t>680962.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-29.69</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>222695</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>178.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>695.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>414.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>128.4</t>
+          <t>129.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>129.98</v>
+        <v>129.75</v>
       </c>
       <c r="AN13" t="n">
-        <v>135.32</v>
+        <v>135.05</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>131.49</t>
+          <t>131.64</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-132.00</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>81276.39999999999</v>
+        <v>76892.39999999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>88237.7</t>
+          <t>88645.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>202045.58</v>
+        <v>198681.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-6961</t>
+          <t>-11752</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-15158.73034348174</t>
+          <t>-15323.1109294538</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-18324.21501716781</t>
+          <t>-16227.2041523001</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>130.2</v>
+        <v>129.98</v>
       </c>
       <c r="AN14" t="n">
-        <v>135.62</v>
+        <v>135.32</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>131.31</t>
+          <t>131.49</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-133.84</t>
+          <t>-132.00</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>94407.39999999999</v>
+        <v>81276.39999999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>91269.6</t>
+          <t>88237.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>207737.7</v>
+        <v>202045.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>-6961</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-14583.18767553882</t>
+          <t>-15158.73034348174</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-16787.68714493714</t>
+          <t>-18324.21501716781</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>130.0</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>129.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>771.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>130.43</v>
+        <v>130.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>135.91</v>
+        <v>135.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>131.31</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.80</t>
+          <t>-133.84</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>94759.8</v>
+        <v>94407.39999999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>99059.1</t>
+          <t>91269.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>221528.96</v>
+        <v>207737.7</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4299</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-14182.36959019367</t>
+          <t>-14583.18767553882</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-16737.5513580027</t>
+          <t>-16787.68714493714</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,69 +6918,69 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>0</t>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>130.57</v>
+        <v>130.43</v>
       </c>
       <c r="AN16" t="n">
-        <v>136.32</v>
+        <v>135.91</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>98412.60000000001</v>
+        <v>94759.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>232237.94</v>
+        <v>221528.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,27 +7464,27 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -7494,43 +7494,43 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>131</v>
+        <v>130.57</v>
       </c>
       <c r="AN17" t="n">
-        <v>136.86</v>
+        <v>136.32</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>100397.6</v>
+        <v>98412.60000000001</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>246240.56</v>
+        <v>232237.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>131.57</v>
+        <v>131</v>
       </c>
       <c r="AN18" t="n">
-        <v>137.37</v>
+        <v>136.86</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>95199</v>
+        <v>100397.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>258672.3</v>
+        <v>246240.56</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>132.12</v>
+        <v>131.57</v>
       </c>
       <c r="AN19" t="n">
-        <v>137.82</v>
+        <v>137.37</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>88131.8</v>
+        <v>95199</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>276222.6</v>
+        <v>258672.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>132.65</v>
+        <v>132.12</v>
       </c>
       <c r="AN20" t="n">
-        <v>138.22</v>
+        <v>137.82</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>103358.4</v>
+        <v>88131.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>306194.04</v>
+        <v>276222.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>133.05</v>
+        <v>132.65</v>
       </c>
       <c r="AN21" t="n">
-        <v>138.55</v>
+        <v>138.22</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>142080</v>
+        <v>103358.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>332412.34</v>
+        <v>306194.04</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>133.22</v>
+        <v>133.05</v>
       </c>
       <c r="AN22" t="n">
-        <v>138.53</v>
+        <v>138.55</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>406545.9514285715</t>
+          <t>406159.7417974322</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>193806</v>
+        <v>142080</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>340328.8</v>
+        <v>332412.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-9640.640469615755</t>
+          <t>-15379.43437848878</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>680.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,219 +10044,219 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>133.22</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>138.53</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>130.33</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-69.86</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-115.80</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>406159.7417974322</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>193806</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>178972.6</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>340328.8</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>14833</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-8794.321600106972</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-9640.640469615755</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>86469.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>120.5</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>振曜</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>3.377018673860202</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>37.82067205908043</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>18.0886033319889</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-3.56</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>138.43</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-66.76</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-113.04</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>406545.9514285715</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>224557.2</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>177976.4</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>352282.84</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>46580</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-8640.445442014467</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-2763.376297310897</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>84668.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>120.5</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>振曜</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>3.377018673860202</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>37.82067205908043</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>18.0886033319889</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
-      </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3058.0</t>
+          <t>3439.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-49.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-24.42</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>11.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>94.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>193.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>190.02</v>
+        <v>189.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>212.73</v>
+        <v>211.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>226.93</t>
+          <t>226.61</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-179.29</t>
+          <t>-172.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>589915.0</t>
+          <t>669415.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1455218</v>
+        <v>856825.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1724547.4</t>
+          <t>1682118.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1071590.52</v>
+        <v>1067307.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-269329</t>
+          <t>-825292</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>124148.6776258694</t>
+          <t>93916.56973940822</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-15925.85478258738</t>
+          <t>-72360.02363612852</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>589915.0</t>
+          <t>669415.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.83</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>197.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>195.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>192.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3911.0</t>
+          <t>3058.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>193.8</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>191.02</v>
+        <v>190.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>213.64</v>
+        <v>212.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>227.21</t>
+          <t>226.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-185.57</t>
+          <t>-179.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2507368.4</v>
+        <v>1455218</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1733652.1</t>
+          <t>1724547.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1072476.02</v>
+        <v>1071590.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>773716</t>
+          <t>-269329</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>149616.774427407</t>
+          <t>124148.6776258694</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>73781.02410756378</t>
+          <t>-15925.85478258738</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4936.0</t>
+          <t>3911.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>92.73</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>192.2</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>191.62</v>
+        <v>191.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>214.64</v>
+        <v>213.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>227.42</t>
+          <t>227.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-191.94</t>
+          <t>-185.57</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2531889.4</v>
+        <v>2507368.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1733241.3</t>
+          <t>1733652.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1067656.78</v>
+        <v>1072476.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>798648</t>
+          <t>773716</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>163405.0926673785</t>
+          <t>149616.774427407</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>181494.8502325097</t>
+          <t>73781.02410756378</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.02</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>190.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>193.5</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>197.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>194.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6845.0</t>
+          <t>4936.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>92.73</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-10.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>192.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>192.22</v>
+        <v>191.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>215.57</v>
+        <v>214.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>227.57</t>
+          <t>227.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-197.91</t>
+          <t>-191.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2544647</v>
+        <v>2531889.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1760186.1</t>
+          <t>1733241.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1063589.72</v>
+        <v>1067656.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>784460</t>
+          <t>798648</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>160116.0458373547</t>
+          <t>163405.0926673785</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>307065.1071884141</t>
+          <t>181494.8502325097</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-24.02</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>193</v>
+        <v>192.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>216.61</v>
+        <v>215.57</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2507410.2</v>
+        <v>2544647</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1052280.38</v>
+        <v>1063589.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>194.1</v>
+        <v>193</v>
       </c>
       <c r="AN7" t="n">
-        <v>217.7</v>
+        <v>216.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1993876.8</v>
+        <v>2507410.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>998034.7</v>
+        <v>1052280.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>195.25</v>
+        <v>194.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>218.81</v>
+        <v>217.7</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>959935.8</v>
+        <v>1993876.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>889723.42</v>
+        <v>998034.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>196.9</v>
+        <v>195.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>220.1</v>
+        <v>218.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>934593.2</v>
+        <v>959935.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>885517.86</v>
+        <v>889723.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>199.58</v>
+        <v>196.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>221.65</v>
+        <v>220.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>975725.2</v>
+        <v>934593.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>877001.76</v>
+        <v>885517.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>202.12</v>
+        <v>199.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>223.18</v>
+        <v>221.65</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1021235.4</v>
+        <v>975725.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>879871.3199999999</v>
+        <v>877001.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3781.0</t>
+          <t>6101.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-32.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>182.3</t>
+          <t>180.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>204.22</v>
+        <v>202.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>224.64</v>
+        <v>223.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>229.71</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.94</t>
+          <t>-20.38</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-191.05</t>
+          <t>-195.94</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2591812.630527818</t>
+          <t>2589550.963675214</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1312241.6</v>
+        <v>1021235.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1102565.0</t>
+          <t>1108546.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>886581.5</v>
+        <v>879871.3199999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>209676</t>
+          <t>-87310</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>45966.15308473548</t>
+          <t>40931.74044305029</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11727.69617533358</t>
+          <t>13242.47091378178</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>680962.0</t>
+          <t>1093709.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>-31.64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>178.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>469.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>129.4</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>129.75</v>
+        <v>129.52</v>
       </c>
       <c r="AN13" t="n">
-        <v>135.05</v>
+        <v>134.8</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>131.64</t>
+          <t>131.79</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-126.93</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>90542.0</t>
+          <t>61876.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>76892.39999999999</v>
+        <v>77067.39999999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>88645.0</t>
+          <t>87740.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>198681.12</v>
+        <v>196606.3</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-11752</t>
+          <t>-10672</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-15323.1109294538</t>
+          <t>-15504.71947001247</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-16227.2041523001</t>
+          <t>-16503.56644308519</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>90542.0</t>
+          <t>61876.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>128.4</t>
+          <t>129.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>129.98</v>
+        <v>129.75</v>
       </c>
       <c r="AN14" t="n">
-        <v>135.32</v>
+        <v>135.05</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>131.49</t>
+          <t>131.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-132.00</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>81276.39999999999</v>
+        <v>76892.39999999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>88237.7</t>
+          <t>88645.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>202045.58</v>
+        <v>198681.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6961</t>
+          <t>-11752</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-15158.73034348174</t>
+          <t>-15323.1109294538</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-18324.21501716781</t>
+          <t>-16227.2041523001</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,102 +6498,102 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-7.89</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>-0.38</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>118.5</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>5.38</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>0.79</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>130.2</v>
+        <v>129.98</v>
       </c>
       <c r="AN15" t="n">
-        <v>135.62</v>
+        <v>135.32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>131.31</t>
+          <t>131.49</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-133.84</t>
+          <t>-132.00</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>94407.39999999999</v>
+        <v>81276.39999999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>91269.6</t>
+          <t>88237.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>207737.7</v>
+        <v>202045.58</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>-6961</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-14583.18767553882</t>
+          <t>-15158.73034348174</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-16787.68714493714</t>
+          <t>-18324.21501716781</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>130.0</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>129.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>771.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>130.43</v>
+        <v>130.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>135.91</v>
+        <v>135.62</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>131.31</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.80</t>
+          <t>-133.84</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>94759.8</v>
+        <v>94407.39999999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>99059.1</t>
+          <t>91269.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>221528.96</v>
+        <v>207737.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4299</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-14182.36959019367</t>
+          <t>-14583.18767553882</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-16737.5513580027</t>
+          <t>-16787.68714493714</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,69 +7348,69 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>0</t>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>130.57</v>
+        <v>130.43</v>
       </c>
       <c r="AN17" t="n">
-        <v>136.32</v>
+        <v>135.91</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>98412.60000000001</v>
+        <v>94759.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>232237.94</v>
+        <v>221528.96</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,22 +7899,22 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -7924,43 +7924,43 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>131</v>
+        <v>130.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>136.86</v>
+        <v>136.32</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>100397.6</v>
+        <v>98412.60000000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>246240.56</v>
+        <v>232237.94</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8151,17 +8151,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>131.57</v>
+        <v>131</v>
       </c>
       <c r="AN19" t="n">
-        <v>137.37</v>
+        <v>136.86</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>95199</v>
+        <v>100397.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>258672.3</v>
+        <v>246240.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>132.12</v>
+        <v>131.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>137.82</v>
+        <v>137.37</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>88131.8</v>
+        <v>95199</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>276222.6</v>
+        <v>258672.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>132.65</v>
+        <v>132.12</v>
       </c>
       <c r="AN21" t="n">
-        <v>138.22</v>
+        <v>137.82</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>103358.4</v>
+        <v>88131.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>306194.04</v>
+        <v>276222.6</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>133.05</v>
+        <v>132.65</v>
       </c>
       <c r="AN22" t="n">
-        <v>138.55</v>
+        <v>138.22</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>142080</v>
+        <v>103358.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>332412.34</v>
+        <v>306194.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>680.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>-17.62</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>469</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>133.22</v>
+        <v>133.05</v>
       </c>
       <c r="AN23" t="n">
-        <v>138.53</v>
+        <v>138.55</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>130.33</t>
+          <t>130.49</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-69.86</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-118.64</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>406159.7417974322</t>
+          <t>405713.3803418804</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>193806</v>
+        <v>142080</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>178972.6</t>
+          <t>172461.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>340328.8</v>
+        <v>332412.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>-30381</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-8794.321600106972</t>
+          <t>-9807.415873704173</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-9640.640469615755</t>
+          <t>-15379.43437848878</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>86469.0</t>
+          <t>70926.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3439.0</t>
+          <t>3226.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-49.06</t>
+          <t>-55.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.42</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>94.55</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>79.09</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>193.7</t>
+          <t>193.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>189.3</v>
+        <v>188.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>211.76</v>
+        <v>210.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>226.61</t>
+          <t>226.27</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-172.80</t>
+          <t>-166.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>669415.0</t>
+          <t>622117.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>856825.8</v>
+        <v>719462.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1682118.0</t>
+          <t>1632054.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1067307.76</v>
+        <v>1064127.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-825292</t>
+          <t>-912592</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>93916.56973940822</t>
+          <t>61990.59112677556</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-72360.02363612852</t>
+          <t>-113602.291242704</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>669415.0</t>
+          <t>622117.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-23.83</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3058.0</t>
+          <t>3439.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-49.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-24.42</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>11.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,63 +1454,63 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>94.55</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>193.7</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>190.02</v>
+        <v>189.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>212.73</v>
+        <v>211.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>226.93</t>
+          <t>226.61</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-179.29</t>
+          <t>-172.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>589915.0</t>
+          <t>669415.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1455218</v>
+        <v>856825.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1724547.4</t>
+          <t>1682118.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1071590.52</v>
+        <v>1067307.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-269329</t>
+          <t>-825292</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>124148.6776258694</t>
+          <t>93916.56973940822</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-15925.85478258738</t>
+          <t>-72360.02363612852</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>589915.0</t>
+          <t>669415.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>197.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>195.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>192.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3911.0</t>
+          <t>3058.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>193.8</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>191.02</v>
+        <v>190.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>213.64</v>
+        <v>212.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>227.21</t>
+          <t>226.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-185.57</t>
+          <t>-179.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2507368.4</v>
+        <v>1455218</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1733652.1</t>
+          <t>1724547.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1072476.02</v>
+        <v>1071590.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>773716</t>
+          <t>-269329</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>149616.774427407</t>
+          <t>124148.6776258694</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>73781.02410756378</t>
+          <t>-15925.85478258738</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4936.0</t>
+          <t>3911.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>92.73</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>192.2</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>191.62</v>
+        <v>191.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>214.64</v>
+        <v>213.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>227.42</t>
+          <t>227.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-191.94</t>
+          <t>-185.57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2531889.4</v>
+        <v>2507368.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1733241.3</t>
+          <t>1733652.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1067656.78</v>
+        <v>1072476.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>798648</t>
+          <t>773716</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>163405.0926673785</t>
+          <t>149616.774427407</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>181494.8502325097</t>
+          <t>73781.02410756378</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.02</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>190.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>193.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>197.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>194.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6845.0</t>
+          <t>4936.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>92.73</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-10.72</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>192.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>192.22</v>
+        <v>191.62</v>
       </c>
       <c r="AN6" t="n">
-        <v>215.57</v>
+        <v>214.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>227.57</t>
+          <t>227.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-197.91</t>
+          <t>-191.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2544647</v>
+        <v>2531889.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1760186.1</t>
+          <t>1733241.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1063589.72</v>
+        <v>1067656.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>784460</t>
+          <t>798648</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>160116.0458373547</t>
+          <t>163405.0926673785</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>307065.1071884141</t>
+          <t>181494.8502325097</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-24.02</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>193</v>
+        <v>192.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>216.61</v>
+        <v>215.57</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2507410.2</v>
+        <v>2544647</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1052280.38</v>
+        <v>1063589.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>194.1</v>
+        <v>193</v>
       </c>
       <c r="AN8" t="n">
-        <v>217.7</v>
+        <v>216.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1993876.8</v>
+        <v>2507410.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>998034.7</v>
+        <v>1052280.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>195.25</v>
+        <v>194.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>218.81</v>
+        <v>217.7</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>959935.8</v>
+        <v>1993876.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>889723.42</v>
+        <v>998034.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>196.9</v>
+        <v>195.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>220.1</v>
+        <v>218.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>934593.2</v>
+        <v>959935.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>885517.86</v>
+        <v>889723.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>199.58</v>
+        <v>196.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>221.65</v>
+        <v>220.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>975725.2</v>
+        <v>934593.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>877001.76</v>
+        <v>885517.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6101.0</t>
+          <t>6515.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-12.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-32.17</t>
+          <t>-33.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.80</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>180.3</t>
+          <t>178.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>202.12</v>
+        <v>199.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>223.18</v>
+        <v>221.65</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>229.71</t>
+          <t>229.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.38</t>
+          <t>-20.03</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-195.94</t>
+          <t>-201.00</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2589550.963675214</t>
+          <t>2587194.810810811</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1021235.4</v>
+        <v>975725.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1108546.1</t>
+          <t>1112681.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>879871.3199999999</v>
+        <v>877001.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-87310</t>
+          <t>-136956</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40931.74044305029</t>
+          <t>37119.13829148119</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>13242.47091378178</t>
+          <t>16149.8264578511</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1093709.0</t>
+          <t>1122750.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>172.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>174.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>469.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>93.57</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>131.1</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>129.52</v>
+        <v>129.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>134.8</v>
+        <v>134.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>131.79</t>
+          <t>131.95</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.93</t>
+          <t>-124.09</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>61876.0</t>
+          <t>85310.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>77067.39999999999</v>
+        <v>74408.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>87740.0</t>
+          <t>84584.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>196606.3</v>
+        <v>190084.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-10672</t>
+          <t>-10175</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-15504.71947001247</t>
+          <t>-15354.28276471173</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-16503.56644308519</t>
+          <t>-14526.88088555762</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>61876.0</t>
+          <t>85310.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>130.5</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>469.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,17 +6174,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>129.4</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>129.75</v>
+        <v>129.52</v>
       </c>
       <c r="AN14" t="n">
-        <v>135.05</v>
+        <v>134.8</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>131.64</t>
+          <t>131.79</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-126.93</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>90542.0</t>
+          <t>61876.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>76892.39999999999</v>
+        <v>77067.39999999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>88645.0</t>
+          <t>87740.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>198681.12</v>
+        <v>196606.3</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-11752</t>
+          <t>-10672</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-15323.1109294538</t>
+          <t>-15504.71947001247</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-16227.2041523001</t>
+          <t>-16503.56644308519</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>90542.0</t>
+          <t>61876.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>128.4</t>
+          <t>129.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>129.98</v>
+        <v>129.75</v>
       </c>
       <c r="AN15" t="n">
-        <v>135.32</v>
+        <v>135.05</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>131.49</t>
+          <t>131.64</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-132.00</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>81276.39999999999</v>
+        <v>76892.39999999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>88237.7</t>
+          <t>88645.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>202045.58</v>
+        <v>198681.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6961</t>
+          <t>-11752</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-15158.73034348174</t>
+          <t>-15323.1109294538</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-18324.21501716781</t>
+          <t>-16227.2041523001</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>130.2</v>
+        <v>129.98</v>
       </c>
       <c r="AN16" t="n">
-        <v>135.62</v>
+        <v>135.32</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>131.31</t>
+          <t>131.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-133.84</t>
+          <t>-132.00</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>94407.39999999999</v>
+        <v>81276.39999999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>91269.6</t>
+          <t>88237.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>207737.7</v>
+        <v>202045.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>-6961</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-14583.18767553882</t>
+          <t>-15158.73034348174</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-16787.68714493714</t>
+          <t>-18324.21501716781</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>130.0</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>129.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>771.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>130.43</v>
+        <v>130.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>135.91</v>
+        <v>135.62</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>131.31</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.80</t>
+          <t>-133.84</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>94759.8</v>
+        <v>94407.39999999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>99059.1</t>
+          <t>91269.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>221528.96</v>
+        <v>207737.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4299</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-14182.36959019367</t>
+          <t>-14583.18767553882</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-16737.5513580027</t>
+          <t>-16787.68714493714</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,69 +7778,69 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>0</t>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>130.57</v>
+        <v>130.43</v>
       </c>
       <c r="AN18" t="n">
-        <v>136.32</v>
+        <v>135.91</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>98412.60000000001</v>
+        <v>94759.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>232237.94</v>
+        <v>221528.96</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,27 +8324,27 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -8354,43 +8354,43 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>131</v>
+        <v>130.57</v>
       </c>
       <c r="AN19" t="n">
-        <v>136.86</v>
+        <v>136.32</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>100397.6</v>
+        <v>98412.60000000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>246240.56</v>
+        <v>232237.94</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>131.57</v>
+        <v>131</v>
       </c>
       <c r="AN20" t="n">
-        <v>137.37</v>
+        <v>136.86</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>95199</v>
+        <v>100397.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>258672.3</v>
+        <v>246240.56</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>132.12</v>
+        <v>131.57</v>
       </c>
       <c r="AN21" t="n">
-        <v>137.82</v>
+        <v>137.37</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>88131.8</v>
+        <v>95199</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>276222.6</v>
+        <v>258672.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>132.65</v>
+        <v>132.12</v>
       </c>
       <c r="AN22" t="n">
-        <v>138.22</v>
+        <v>137.82</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>103358.4</v>
+        <v>88131.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>306194.04</v>
+        <v>276222.6</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>133.05</v>
+        <v>132.65</v>
       </c>
       <c r="AN23" t="n">
-        <v>138.55</v>
+        <v>138.22</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>130.49</t>
+          <t>130.58</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-67.48</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-118.64</t>
+          <t>-122.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>405713.3803418804</t>
+          <t>405318.2901849218</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>142080</v>
+        <v>103358.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>172461.5</t>
+          <t>167750.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>332412.34</v>
+        <v>306194.04</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-30381</t>
+          <t>-64391</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-9807.415873704173</t>
+          <t>-10693.3987016324</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-15379.43437848878</t>
+          <t>-15566.30425523766</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>70926.0</t>
+          <t>116870.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3226.0</t>
+          <t>5495.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-55.92</t>
+          <t>-54.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.09</t>
+          <t>51.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>193.4</t>
+          <t>192.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>188.55</v>
+        <v>187.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>210.8</v>
+        <v>209.75</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>226.27</t>
+          <t>225.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-166.77</t>
+          <t>-161.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>622117.0</t>
+          <t>1040079.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>719462.4</v>
+        <v>735522</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1632054.7</t>
+          <t>1633705.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1064127.48</v>
+        <v>1076294.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-912592</t>
+          <t>-898183</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>61990.59112677556</t>
+          <t>35794.39690938866</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-113602.291242704</t>
+          <t>-108284.6712862393</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>622117.0</t>
+          <t>1040079.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-26.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>187.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3439.0</t>
+          <t>3226.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-49.06</t>
+          <t>-55.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.42</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.55</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>79.09</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>193.7</t>
+          <t>193.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>189.3</v>
+        <v>188.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>211.76</v>
+        <v>210.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>226.61</t>
+          <t>226.27</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-172.80</t>
+          <t>-166.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>669415.0</t>
+          <t>622117.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>856825.8</v>
+        <v>719462.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1682118.0</t>
+          <t>1632054.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1067307.76</v>
+        <v>1064127.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-825292</t>
+          <t>-912592</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>93916.56973940822</t>
+          <t>61990.59112677556</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-72360.02363612852</t>
+          <t>-113602.291242704</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>669415.0</t>
+          <t>622117.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-23.83</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3058.0</t>
+          <t>3439.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-49.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-24.42</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>11.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>94.55</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>193.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>190.02</v>
+        <v>189.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>212.73</v>
+        <v>211.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>226.93</t>
+          <t>226.61</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-179.29</t>
+          <t>-172.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>589915.0</t>
+          <t>669415.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1455218</v>
+        <v>856825.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1724547.4</t>
+          <t>1682118.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1071590.52</v>
+        <v>1067307.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-269329</t>
+          <t>-825292</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>124148.6776258694</t>
+          <t>93916.56973940822</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-15925.85478258738</t>
+          <t>-72360.02363612852</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>589915.0</t>
+          <t>669415.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-23.83</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>197.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>195.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>192.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3911.0</t>
+          <t>3058.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>193.8</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>191.02</v>
+        <v>190.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>213.64</v>
+        <v>212.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>227.21</t>
+          <t>226.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-185.57</t>
+          <t>-179.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2507368.4</v>
+        <v>1455218</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1733652.1</t>
+          <t>1724547.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1072476.02</v>
+        <v>1071590.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>773716</t>
+          <t>-269329</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>149616.774427407</t>
+          <t>124148.6776258694</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>73781.02410756378</t>
+          <t>-15925.85478258738</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>756084.0</t>
+          <t>589915.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4936.0</t>
+          <t>3911.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>194.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>44.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>92.73</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>192.2</t>
+          <t>193.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>191.62</v>
+        <v>191.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>214.64</v>
+        <v>213.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>227.42</t>
+          <t>227.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-191.94</t>
+          <t>-185.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2531889.4</v>
+        <v>2507368.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1733241.3</t>
+          <t>1733652.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1067656.78</v>
+        <v>1072476.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>798648</t>
+          <t>773716</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>163405.0926673785</t>
+          <t>149616.774427407</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>181494.8502325097</t>
+          <t>73781.02410756378</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>959781.0</t>
+          <t>756084.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-24.02</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>190.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>193.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>197.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>194.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6845.0</t>
+          <t>4936.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>92.73</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-10.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>192.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>192.22</v>
+        <v>191.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>215.57</v>
+        <v>214.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>227.57</t>
+          <t>227.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-10.95</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-197.91</t>
+          <t>-191.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2544647</v>
+        <v>2531889.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1760186.1</t>
+          <t>1733241.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1063589.72</v>
+        <v>1067656.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>784460</t>
+          <t>798648</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>160116.0458373547</t>
+          <t>163405.0926673785</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>307065.1071884141</t>
+          <t>181494.8502325097</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1308934.0</t>
+          <t>959781.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-24.41</t>
+          <t>-24.02</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>190.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>194.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19044.0</t>
+          <t>6845.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>63.37</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>187.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>193</v>
+        <v>192.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>216.61</v>
+        <v>215.57</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227.57</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-202.83</t>
+          <t>-197.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2507410.2</v>
+        <v>2544647</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1764322.8</t>
+          <t>1760186.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1052280.38</v>
+        <v>1063589.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>743087</t>
+          <t>784460</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>133398.0346826167</t>
+          <t>160116.0458373547</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>438075.3275829772</t>
+          <t>307065.1071884141</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3661376.0</t>
+          <t>1308934.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-24.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>193.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30052.0</t>
+          <t>19044.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>63.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>179.4</t>
+          <t>182.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>194.1</v>
+        <v>193</v>
       </c>
       <c r="AN9" t="n">
-        <v>217.7</v>
+        <v>216.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>228.03</t>
+          <t>227.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-9.96</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-206.27</t>
+          <t>-202.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1993876.8</v>
+        <v>2507410.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1653059.2</t>
+          <t>1764322.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>998034.7</v>
+        <v>1052280.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>743087</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>78002.1632461875</t>
+          <t>133398.0346826167</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>357539.880732961</t>
+          <t>438075.3275829772</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5850667.0</t>
+          <t>3661376.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-23.24</t>
+          <t>-25.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>188.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4737.0</t>
+          <t>30052.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.90</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.10</t>
+          <t>-23.84</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>176.1</t>
+          <t>179.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>195.25</v>
+        <v>194.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>218.81</v>
+        <v>217.7</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>228.25</t>
+          <t>228.03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-207.99</t>
+          <t>-206.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>959935.8</v>
+        <v>1993876.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1169164.2</t>
+          <t>1653059.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>889723.42</v>
+        <v>998034.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-209228</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>27177.12370313777</t>
+          <t>78002.1632461875</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-4846.931936096633</t>
+          <t>357539.880732961</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>878689.0</t>
+          <t>5850667.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>-23.24</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>201.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6026.0</t>
+          <t>4737.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.12</t>
+          <t>-17.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.50</t>
+          <t>-28.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>-10.77</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>176.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>196.9</v>
+        <v>195.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>220.1</v>
+        <v>218.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>228.61</t>
+          <t>228.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>-12.98</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-205.95</t>
+          <t>-207.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>934593.2</v>
+        <v>959935.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1141409.6</t>
+          <t>1169164.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>885517.86</v>
+        <v>889723.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-206816</t>
+          <t>-209228</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32999.67927390766</t>
+          <t>27177.12370313777</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>10342.65467725322</t>
+          <t>-4846.931936096633</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1023569.0</t>
+          <t>878689.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-27.54</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>185.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6515.0</t>
+          <t>6026.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.31</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-34.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.96</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>178.2</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>199.58</v>
+        <v>196.9</v>
       </c>
       <c r="AN12" t="n">
-        <v>221.65</v>
+        <v>220.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>229.15</t>
+          <t>228.61</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.03</t>
+          <t>-18.71</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-14.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-201.00</t>
+          <t>-205.95</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2587194.810810811</t>
+          <t>2585735.895596591</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>975725.2</v>
+        <v>934593.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1112681.5</t>
+          <t>1141409.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>877001.76</v>
+        <v>885517.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-136956</t>
+          <t>-206816</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>37119.13829148119</t>
+          <t>32999.67927390766</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>16149.8264578511</t>
+          <t>10342.65467725322</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1122750.0</t>
+          <t>1023569.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-33.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>172.5</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>174.5</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>368.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>93.57</t>
+          <t>80.95</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>131.1</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>129.25</v>
+        <v>128.85</v>
       </c>
       <c r="AN13" t="n">
-        <v>134.62</v>
+        <v>134.45</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>131.95</t>
+          <t>132.07</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>42.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-124.09</t>
+          <t>-121.75</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>85310.0</t>
+          <t>47927.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>74408.2</v>
+        <v>68000.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>84584.0</t>
+          <t>81204.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>190084.18</v>
+        <v>186435.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-10175</t>
+          <t>-13203</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-15354.28276471173</t>
+          <t>-15389.58602754829</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-14526.88088555762</t>
+          <t>-15583.75397314939</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>85310.0</t>
+          <t>47927.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>469.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>93.57</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>131.1</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>129.52</v>
+        <v>129.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>134.8</v>
+        <v>134.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>131.79</t>
+          <t>131.95</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-126.93</t>
+          <t>-124.09</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>61876.0</t>
+          <t>85310.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>77067.39999999999</v>
+        <v>74408.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>87740.0</t>
+          <t>84584.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>196606.3</v>
+        <v>190084.18</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-10672</t>
+          <t>-10175</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-15504.71947001247</t>
+          <t>-15354.28276471173</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-16503.56644308519</t>
+          <t>-14526.88088555762</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>61876.0</t>
+          <t>85310.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>130.5</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>469.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,17 +6604,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>129.4</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>129.75</v>
+        <v>129.52</v>
       </c>
       <c r="AN15" t="n">
-        <v>135.05</v>
+        <v>134.8</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>131.64</t>
+          <t>131.79</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-126.93</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>90542.0</t>
+          <t>61876.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>76892.39999999999</v>
+        <v>77067.39999999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>88645.0</t>
+          <t>87740.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>198681.12</v>
+        <v>196606.3</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-11752</t>
+          <t>-10672</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-15323.1109294538</t>
+          <t>-15504.71947001247</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-16227.2041523001</t>
+          <t>-16503.56644308519</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>90542.0</t>
+          <t>61876.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>128.4</t>
+          <t>129.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>129.98</v>
+        <v>129.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>135.32</v>
+        <v>135.05</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>131.49</t>
+          <t>131.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-132.00</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>81276.39999999999</v>
+        <v>76892.39999999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>88237.7</t>
+          <t>88645.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>202045.58</v>
+        <v>198681.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-6961</t>
+          <t>-11752</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-15158.73034348174</t>
+          <t>-15323.1109294538</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-18324.21501716781</t>
+          <t>-16227.2041523001</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>54349.0</t>
+          <t>90542.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>130.2</v>
+        <v>129.98</v>
       </c>
       <c r="AN17" t="n">
-        <v>135.62</v>
+        <v>135.32</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>131.31</t>
+          <t>131.49</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-133.84</t>
+          <t>-132.00</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>94407.39999999999</v>
+        <v>81276.39999999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>91269.6</t>
+          <t>88237.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>207737.7</v>
+        <v>202045.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>-6961</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-14583.18767553882</t>
+          <t>-15158.73034348174</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-16787.68714493714</t>
+          <t>-18324.21501716781</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>79964.0</t>
+          <t>54349.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>130.0</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>129.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>771.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>130.43</v>
+        <v>130.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>135.91</v>
+        <v>135.62</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>131.12</t>
+          <t>131.31</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-134.80</t>
+          <t>-133.84</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>94759.8</v>
+        <v>94407.39999999999</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>99059.1</t>
+          <t>91269.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>221528.96</v>
+        <v>207737.7</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4299</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-14182.36959019367</t>
+          <t>-14583.18767553882</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-16737.5513580027</t>
+          <t>-16787.68714493714</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>98606.0</t>
+          <t>79964.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>489.0</t>
+          <t>771.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,69 +8208,69 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-18.16</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>0</t>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>130.57</v>
+        <v>130.43</v>
       </c>
       <c r="AN19" t="n">
-        <v>136.32</v>
+        <v>135.91</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>130.96</t>
+          <t>131.12</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-22.40</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-134.38</t>
+          <t>-134.80</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>98412.60000000001</v>
+        <v>94759.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>120246.3</t>
+          <t>99059.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>232237.94</v>
+        <v>221528.96</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-21833</t>
+          <t>-4299</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-13717.79108695567</t>
+          <t>-14182.36959019367</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-18065.51625673911</t>
+          <t>-16737.5513580027</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>61001.0</t>
+          <t>98606.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>489.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-31.75</t>
+          <t>-18.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,27 +8754,27 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -8784,43 +8784,43 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>131</v>
+        <v>130.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>136.86</v>
+        <v>136.32</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>130.86</t>
+          <t>130.96</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-30.54</t>
+          <t>-22.40</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-132.45</t>
+          <t>-134.38</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>100397.6</v>
+        <v>98412.60000000001</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>147101.8</t>
+          <t>120246.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>246240.56</v>
+        <v>232237.94</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-46704</t>
+          <t>-21833</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-12927.2956015405</t>
+          <t>-13717.79108695567</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-15288.3048171933</t>
+          <t>-18065.51625673911</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>112462.0</t>
+          <t>61001.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>951.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-31.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>124.6</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>131.57</v>
+        <v>131</v>
       </c>
       <c r="AN21" t="n">
-        <v>137.37</v>
+        <v>136.86</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>130.75</t>
+          <t>130.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-132.45</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>95199</v>
+        <v>100397.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>159878.1</t>
+          <t>147101.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>258672.3</v>
+        <v>246240.56</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-64679</t>
+          <t>-46704</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-12498.02119869453</t>
+          <t>-12927.2956015405</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-16288.52758865671</t>
+          <t>-15288.3048171933</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>120004.0</t>
+          <t>112462.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>951.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>124.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>132.12</v>
+        <v>131.57</v>
       </c>
       <c r="AN22" t="n">
-        <v>137.82</v>
+        <v>137.37</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>130.75</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-64.92</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-126.76</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>88131.8</v>
+        <v>95199</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>160897.0</t>
+          <t>159878.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>276222.6</v>
+        <v>258672.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-72765</t>
+          <t>-64679</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-11808.83821870141</t>
+          <t>-12498.02119869453</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-17943.75556258095</t>
+          <t>-16288.52758865671</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>81726.0</t>
+          <t>120004.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>668.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-45.22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>132.65</v>
+        <v>132.12</v>
       </c>
       <c r="AN23" t="n">
-        <v>138.22</v>
+        <v>137.82</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>130.58</t>
+          <t>130.63</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-67.48</t>
+          <t>-64.92</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-122.42</t>
+          <t>-126.76</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>405318.2901849218</t>
+          <t>404844.6711647727</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>103358.4</v>
+        <v>88131.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>167750.0</t>
+          <t>160897.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>306194.04</v>
+        <v>276222.6</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-64391</t>
+          <t>-72765</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-10693.3987016324</t>
+          <t>-11808.83821870141</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-15566.30425523766</t>
+          <t>-17943.75556258095</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>116870.0</t>
+          <t>81726.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電子書.xlsx
+++ b/Result/checksun_type/電子書.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D2" t